--- a/results/Int Task Remove ACC -0.4/Rando_4_permute.xlsx
+++ b/results/Int Task Remove ACC -0.4/Rando_4_permute.xlsx
@@ -440,887 +440,887 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.6932782280258887</v>
+        <v>0.6742496251447225</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>scr_ptp</t>
+          <t>hrv_n_above_mean</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.6993343709074344</v>
+        <v>0.6806312752671437</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>scr_iqr</t>
+          <t>bvp_perm_entropy</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.6868645016797312</v>
+        <v>0.655145292007516</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>scr_rms</t>
+          <t>scr_pct_95</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.6756932450130013</v>
+        <v>0.6594188319699357</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>scl_n_sign_changes</t>
+          <t>hrv_energy</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.6770930210488355</v>
+        <v>0.6677736443524969</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>hrv_pct_5</t>
+          <t>scl_peaks</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.6874969157477177</v>
+        <v>0.6667566951999544</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>scl_pct_5</t>
+          <t>hrv_perm_entropy</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.7029130525556588</v>
+        <v>0.6671985499269268</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
-          <t>bvp_skewness</t>
+          <t>hrv_iqr</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.692050410917304</v>
+        <v>0.6767339191831002</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>bvp_std</t>
+          <t>scl_entropy</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.6879826143071346</v>
+        <v>0.6777491601343785</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="inlineStr">
         <is>
-          <t>bvp_ptp</t>
+          <t>bvp_svd_entropy</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.6917991155313454</v>
+        <v>0.6676673562738437</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="1" t="inlineStr">
         <is>
-          <t>scl_svd_entropy</t>
+          <t>scr_min</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>0.6763391348909598</v>
+        <v>0.6676673562738437</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="1" t="inlineStr">
         <is>
-          <t>hrv_skewness</t>
+          <t>scr_n_above_mean</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>0.6783578491848083</v>
+        <v>0.6685966177614971</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
         <is>
-          <t>scr_std</t>
+          <t>bvp_peaks</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>0.6791825307950727</v>
+        <v>0.6643587602254826</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="1" t="inlineStr">
         <is>
-          <t>hrv_n_sign_changes</t>
+          <t>scl_iqr</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>0.6791825307950727</v>
+        <v>0.653423614933475</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="1" t="inlineStr">
         <is>
-          <t>hrv_kurtosis</t>
+          <t>hrv_lineintegral</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0.678224609486211</v>
+        <v>0.6633182758555242</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="1" t="inlineStr">
         <is>
-          <t>bvp_min</t>
+          <t>hrv_mean</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>0.6900148044109553</v>
+        <v>0.6325636304970865</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="1" t="inlineStr">
         <is>
-          <t>bvp_n_below_mean</t>
+          <t>hrv_sum</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>0.6755937897394044</v>
+        <v>0.6444870651204282</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>scl_lineintegral</t>
+          <t>bvp_kurtosis</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>0.667414352686621</v>
+        <v>0.6507254161368079</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="1" t="inlineStr">
         <is>
-          <t>scl_n_below_mean</t>
+          <t>hrv_rms</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>0.6688310209349555</v>
+        <v>0.6224212803917475</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="1" t="inlineStr">
         <is>
-          <t>bvp_energy</t>
+          <t>scr_kurtosis</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>0.663007573025604</v>
+        <v>0.6223032247043863</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="1" t="inlineStr">
         <is>
-          <t>bvp_pct_95</t>
+          <t>bvp_n_above_mean</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>0.6585165221022264</v>
+        <v>0.6308890238578777</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="1" t="inlineStr">
         <is>
-          <t>bvp_peaks</t>
+          <t>bvp_skewness</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>0.6840044033632585</v>
+        <v>0.6443724258355951</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="1" t="inlineStr">
         <is>
-          <t>scl_kurtosis</t>
+          <t>scl_perm_entropy</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>0.6869523791447606</v>
+        <v>0.6500305578226129</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="1" t="inlineStr">
         <is>
-          <t>scr_mean</t>
+          <t>scl_sum</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>0.6546427012355989</v>
+        <v>0.6343344658075047</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="1" t="inlineStr">
         <is>
-          <t>scl_ptp</t>
+          <t>bvp_pct_5</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>0.6570880862451838</v>
+        <v>0.6483557613832635</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="1" t="inlineStr">
         <is>
-          <t>scr_perm_entropy</t>
+          <t>scl_std</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>0.6529612617913336</v>
+        <v>0.6366836221458804</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="1" t="inlineStr">
         <is>
-          <t>scl_pct_95</t>
+          <t>bvp_std</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>0.6504112969043596</v>
+        <v>0.6353967771936151</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="1" t="inlineStr">
         <is>
-          <t>hrv_iqr</t>
+          <t>scl_pct_95</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>0.6734925123844592</v>
+        <v>0.6425879249150644</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="1" t="inlineStr">
         <is>
-          <t>hrv_entropy</t>
+          <t>hrv_min</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>0.6723136637121112</v>
+        <v>0.6408626416383548</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="1" t="inlineStr">
         <is>
-          <t>scl_n_above_mean</t>
+          <t>hrv_pct_5</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>0.6707368041452351</v>
+        <v>0.6293339913071536</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="1" t="inlineStr">
         <is>
-          <t>scl_rms</t>
+          <t>scl_svd_entropy</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>0.6892476322432479</v>
+        <v>0.6400937612693833</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="1" t="inlineStr">
         <is>
-          <t>scr_entropy</t>
+          <t>scl_ptp</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>0.6892476322432479</v>
+        <v>0.6350949949702962</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="1" t="inlineStr">
         <is>
-          <t>bvp_kurtosis</t>
+          <t>scl_n_above_mean</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>0.6802435135802001</v>
+        <v>0.6334000797160591</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="1" t="inlineStr">
         <is>
-          <t>bvp_n_above_mean</t>
+          <t>scr_rms</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>0.6125260500692771</v>
+        <v>0.647325336420749</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="1" t="inlineStr">
         <is>
-          <t>hrv_mean</t>
+          <t>bvp_mean</t>
         </is>
       </c>
       <c r="B36" t="n">
-        <v>0.6249976274982443</v>
+        <v>0.6489173799988612</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="1" t="inlineStr">
         <is>
-          <t>scr_iqr_5_95</t>
+          <t>scl_kurtosis</t>
         </is>
       </c>
       <c r="B37" t="n">
-        <v>0.6211069144191166</v>
+        <v>0.6490354356862225</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="1" t="inlineStr">
         <is>
-          <t>scr_min</t>
+          <t>scr_svd_entropy</t>
         </is>
       </c>
       <c r="B38" t="n">
-        <v>0.6211069144191166</v>
+        <v>0.6536614345094616</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="1" t="inlineStr">
         <is>
-          <t>bvp_sum</t>
+          <t>hrv_entropy</t>
         </is>
       </c>
       <c r="B39" t="n">
-        <v>0.6211069144191166</v>
+        <v>0.6531892117600168</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="1" t="inlineStr">
         <is>
-          <t>hrv_pct_95</t>
+          <t>scr_perm_entropy</t>
         </is>
       </c>
       <c r="B40" t="n">
-        <v>0.667675897280164</v>
+        <v>0.6604242033139105</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="1" t="inlineStr">
         <is>
-          <t>scr_n_above_mean</t>
+          <t>scr_energy</t>
         </is>
       </c>
       <c r="B41" t="n">
-        <v>0.6623129045115493</v>
+        <v>0.6504908231632092</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="1" t="inlineStr">
         <is>
-          <t>hrv_energy</t>
+          <t>scl_max</t>
         </is>
       </c>
       <c r="B42" t="n">
-        <v>0.6588135593220339</v>
+        <v>0.642928616167176</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="1" t="inlineStr">
         <is>
-          <t>scl_std</t>
+          <t>bvp_n_below_mean</t>
         </is>
       </c>
       <c r="B43" t="n">
-        <v>0.6300134758099721</v>
+        <v>0.6316005845844326</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="1" t="inlineStr">
         <is>
-          <t>hrv_ptp</t>
+          <t>bvp_entropy</t>
         </is>
       </c>
       <c r="B44" t="n">
-        <v>0.6554793402547119</v>
+        <v>0.6316005845844326</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="1" t="inlineStr">
         <is>
-          <t>scr_n_sign_changes</t>
+          <t>scr_entropy</t>
         </is>
       </c>
       <c r="B45" t="n">
-        <v>0.6554793402547119</v>
+        <v>0.6316005845844326</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="1" t="inlineStr">
         <is>
-          <t>scr_pct_5</t>
+          <t>bvp_max</t>
         </is>
       </c>
       <c r="B46" t="n">
-        <v>0.6297452882115133</v>
+        <v>0.6269762939624575</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="1" t="inlineStr">
         <is>
-          <t>bvp_mean</t>
+          <t>scl_iqr_5_95</t>
         </is>
       </c>
       <c r="B47" t="n">
-        <v>0.6301432991060414</v>
+        <v>0.6294250953745706</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="1" t="inlineStr">
         <is>
-          <t>scl_mean</t>
+          <t>scr_pct_5</t>
         </is>
       </c>
       <c r="B48" t="n">
-        <v>0.6235997494638146</v>
+        <v>0.6373481124376033</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="1" t="inlineStr">
         <is>
-          <t>bvp_rms</t>
+          <t>hrv_n_below_mean</t>
         </is>
       </c>
       <c r="B49" t="n">
-        <v>0.6515127071194032</v>
+        <v>0.6287672480877635</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="1" t="inlineStr">
         <is>
-          <t>hrv_iqr_5_95</t>
+          <t>bvp_n_sign_changes</t>
         </is>
       </c>
       <c r="B50" t="n">
-        <v>0.6559312543891282</v>
+        <v>0.6130796970789758</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="1" t="inlineStr">
         <is>
-          <t>hrv_svd_entropy</t>
+          <t>bvp_ptp</t>
         </is>
       </c>
       <c r="B51" t="n">
-        <v>0.6593918803499914</v>
+        <v>0.6301334294987379</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="1" t="inlineStr">
         <is>
-          <t>hrv_n_above_mean</t>
+          <t>scr_std</t>
         </is>
       </c>
       <c r="B52" t="n">
-        <v>0.6593918803499914</v>
+        <v>0.6058986087649705</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="1" t="inlineStr">
         <is>
-          <t>bvp_max</t>
+          <t>scr_n_sign_changes</t>
         </is>
       </c>
       <c r="B53" t="n">
-        <v>0.676175906770171</v>
+        <v>0.6058986087649705</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="1" t="inlineStr">
         <is>
-          <t>bvp_pct_5</t>
+          <t>bvp_sum</t>
         </is>
       </c>
       <c r="B54" t="n">
-        <v>0.6861276975344961</v>
+        <v>0.605559625714123</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="1" t="inlineStr">
         <is>
-          <t>scr_lineintegral</t>
+          <t>scl_n_sign_changes</t>
         </is>
       </c>
       <c r="B55" t="n">
-        <v>0.6550558961413632</v>
+        <v>0.6145637443771709</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="1" t="inlineStr">
         <is>
-          <t>scl_min</t>
+          <t>scr_mean</t>
         </is>
       </c>
       <c r="B56" t="n">
-        <v>0.6514333706606943</v>
+        <v>0.6048512915899558</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="1" t="inlineStr">
         <is>
-          <t>bvp_n_sign_changes</t>
+          <t>hrv_kurtosis</t>
         </is>
       </c>
       <c r="B57" t="n">
-        <v>0.6724975800482091</v>
+        <v>0.6073708884544574</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="1" t="inlineStr">
         <is>
-          <t>scl_max</t>
+          <t>bvp_pct_95</t>
         </is>
       </c>
       <c r="B58" t="n">
-        <v>0.6569616793516426</v>
+        <v>0.6522700096798072</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="1" t="inlineStr">
         <is>
-          <t>bvp_iqr_5_95</t>
+          <t>scl_lineintegral</t>
         </is>
       </c>
       <c r="B59" t="n">
-        <v>0.6873773416592328</v>
+        <v>0.6491128741435268</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="1" t="inlineStr">
         <is>
-          <t>hrv_max</t>
+          <t>bvp_iqr</t>
         </is>
       </c>
       <c r="B60" t="n">
-        <v>0.5568694364833831</v>
+        <v>0.6664564313777592</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="1" t="inlineStr">
         <is>
-          <t>scr_kurtosis</t>
+          <t>hrv_std</t>
         </is>
       </c>
       <c r="B61" t="n">
-        <v>0.5590652343082734</v>
+        <v>0.6635204130051056</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="1" t="inlineStr">
         <is>
-          <t>hrv_std</t>
+          <t>scl_min</t>
         </is>
       </c>
       <c r="B62" t="n">
-        <v>0.5499060489304762</v>
+        <v>0.6721399965835975</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="1" t="inlineStr">
         <is>
-          <t>scr_pct_95</t>
+          <t>scr_n_below_mean</t>
         </is>
       </c>
       <c r="B63" t="n">
-        <v>0.5157209558335073</v>
+        <v>0.6677246759162602</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="1" t="inlineStr">
         <is>
-          <t>bvp_perm_entropy</t>
+          <t>bvp_lineintegral</t>
         </is>
       </c>
       <c r="B64" t="n">
-        <v>0.5096836031658664</v>
+        <v>0.675821549907947</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="1" t="inlineStr">
         <is>
-          <t>hrv_min</t>
+          <t>hrv_pct_95</t>
         </is>
       </c>
       <c r="B65" t="n">
-        <v>0.5504372995236017</v>
+        <v>0.5677556133391539</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="1" t="inlineStr">
         <is>
-          <t>scr_skewness</t>
+          <t>scl_n_below_mean</t>
         </is>
       </c>
       <c r="B66" t="n">
-        <v>0.5531187959079089</v>
+        <v>0.56696471615389</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="1" t="inlineStr">
         <is>
-          <t>scr_energy</t>
+          <t>scr_max</t>
         </is>
       </c>
       <c r="B67" t="n">
-        <v>0.5233034714445689</v>
+        <v>0.5395036726327178</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="1" t="inlineStr">
         <is>
-          <t>scl_skewness</t>
+          <t>bvp_min</t>
         </is>
       </c>
       <c r="B68" t="n">
-        <v>0.5249832026875699</v>
+        <v>0.5349720044792833</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="1" t="inlineStr">
         <is>
-          <t>hrv_rms</t>
+          <t>scr_peaks</t>
         </is>
       </c>
       <c r="B69" t="n">
-        <v>0.5001095146810408</v>
+        <v>0.533277089225046</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="1" t="inlineStr">
         <is>
-          <t>bvp_svd_entropy</t>
+          <t>scl_pct_5</t>
         </is>
       </c>
       <c r="B70" t="n">
-        <v>0.4955273596902461</v>
+        <v>0.5177024692998272</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="1" t="inlineStr">
         <is>
-          <t>scr_peaks</t>
+          <t>scr_lineintegral</t>
         </is>
       </c>
       <c r="B71" t="n">
-        <v>0.4955273596902461</v>
+        <v>0.4980127925294665</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="1" t="inlineStr">
         <is>
-          <t>bvp_lineintegral</t>
+          <t>scl_energy</t>
         </is>
       </c>
       <c r="B72" t="n">
-        <v>0.4953047241254959</v>
+        <v>0.4975236775675214</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="1" t="inlineStr">
         <is>
-          <t>scl_entropy</t>
+          <t>scr_ptp</t>
         </is>
       </c>
       <c r="B73" t="n">
-        <v>0.5087021466395886</v>
+        <v>0.5193552489228842</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="1" t="inlineStr">
         <is>
-          <t>scl_perm_entropy</t>
+          <t>scl_skewness</t>
         </is>
       </c>
       <c r="B74" t="n">
-        <v>0.5074052422798793</v>
+        <v>0.518852658150967</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="1" t="inlineStr">
         <is>
-          <t>scl_energy</t>
+          <t>hrv_max</t>
         </is>
       </c>
       <c r="B75" t="n">
-        <v>0.4987569988801792</v>
+        <v>0.4823491563383757</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="1" t="inlineStr">
         <is>
-          <t>bvp_entropy</t>
+          <t>hrv_skewness</t>
         </is>
       </c>
       <c r="B76" t="n">
-        <v>0.4987569988801792</v>
+        <v>0.4824081841820563</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="1" t="inlineStr">
         <is>
-          <t>scl_sum</t>
+          <t>bvp_iqr_5_95</t>
         </is>
       </c>
       <c r="B77" t="n">
-        <v>0.492567616300036</v>
+        <v>0.4819949892762921</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="1" t="inlineStr">
         <is>
-          <t>hrv_perm_entropy</t>
+          <t>scr_skewness</t>
         </is>
       </c>
       <c r="B78" t="n">
-        <v>0.4929656271945642</v>
+        <v>0.4851352326000721</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="1" t="inlineStr">
         <is>
-          <t>scr_max</t>
+          <t>hrv_peaks</t>
         </is>
       </c>
       <c r="B79" t="n">
-        <v>0.4905471938049234</v>
+        <v>0.4857541708580865</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="1" t="inlineStr">
         <is>
-          <t>scr_sum</t>
+          <t>scl_rms</t>
         </is>
       </c>
       <c r="B80" t="n">
-        <v>0.4993286769032209</v>
+        <v>0.4857811224780306</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="1" t="inlineStr">
         <is>
-          <t>scl_iqr_5_95</t>
+          <t>hrv_n_sign_changes</t>
         </is>
       </c>
       <c r="B81" t="n">
-        <v>0.4976927894926643</v>
+        <v>0.4857811224780306</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="1" t="inlineStr">
         <is>
-          <t>bvp_iqr</t>
+          <t>scl_mean</t>
         </is>
       </c>
       <c r="B82" t="n">
-        <v>0.5263273672822518</v>
+        <v>0.4824789796344449</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" s="1" t="inlineStr">
         <is>
-          <t>scl_iqr</t>
+          <t>bvp_rms</t>
         </is>
       </c>
       <c r="B83" t="n">
-        <v>0.5527238218156282</v>
+        <v>0.4816592328278323</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" s="1" t="inlineStr">
         <is>
-          <t>hrv_lineintegral</t>
+          <t>hrv_ptp</t>
         </is>
       </c>
       <c r="B84" t="n">
-        <v>0.5331220225102966</v>
+        <v>0.4909080038719228</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" s="1" t="inlineStr">
         <is>
-          <t>hrv_peaks</t>
+          <t>bvp_energy</t>
         </is>
       </c>
       <c r="B85" t="n">
-        <v>0.5336380890921859</v>
+        <v>0.490628048664756</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" s="1" t="inlineStr">
         <is>
-          <t>hrv_n_below_mean</t>
+          <t>scr_iqr</t>
         </is>
       </c>
       <c r="B86" t="n">
-        <v>0.5309431168979065</v>
+        <v>0.5090124698692278</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" s="1" t="inlineStr">
         <is>
-          <t>scl_peaks</t>
+          <t>scr_sum</t>
         </is>
       </c>
       <c r="B87" t="n">
-        <v>0.5309431168979065</v>
+        <v>0.5244100062634046</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" s="1" t="inlineStr">
         <is>
-          <t>scr_n_below_mean</t>
+          <t>hrv_svd_entropy</t>
         </is>
       </c>
       <c r="B88" t="n">
-        <v>0.5383772087991345</v>
+        <v>0.5246578852468351</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" s="1" t="inlineStr">
         <is>
-          <t>hrv_sum</t>
+          <t>scr_iqr_5_95</t>
         </is>
       </c>
       <c r="B89" t="n">
-        <v>0.5018818683925826</v>
+        <v>0.5191886043995673</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" s="1" t="inlineStr">
         <is>
-          <t>scr_svd_entropy</t>
+          <t>hrv_iqr_5_95</t>
         </is>
       </c>
       <c r="B90" t="n">
-        <v>0.5085013380909902</v>
+        <v>0.5128559227133828</v>
       </c>
     </row>
   </sheetData>
